--- a/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
+++ b/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\PA\elec\DPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E12590D8-7C6D-4C28-A65F-7E161F97A5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{381D4AB0-7D7E-4CFA-B072-BB0F0BDD3787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="130" yWindow="130" windowWidth="15620" windowHeight="10155" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="1530" windowWidth="16680" windowHeight="16470" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -844,7 +844,7 @@
         <v>106</v>
       </c>
       <c r="C1" s="6">
-        <v>45342</v>
+        <v>45343</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>32</v>
@@ -2018,13 +2018,13 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">

--- a/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
+++ b/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\PA\elec\DPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{381D4AB0-7D7E-4CFA-B072-BB0F0BDD3787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{05340621-D6A9-4183-891D-D036E3EA4B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1530" windowWidth="16680" windowHeight="16470" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="315" yWindow="645" windowWidth="16830" windowHeight="16320" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -844,7 +844,7 @@
         <v>106</v>
       </c>
       <c r="C1" s="6">
-        <v>45343</v>
+        <v>45350</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>32</v>
@@ -3883,94 +3883,94 @@
         <v>13</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">

--- a/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
+++ b/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\PA\elec\DPbES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\PA\elec\DPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C117FDF1-4364-4E60-93F2-01F46E9F6EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4044DF0-D199-4A1A-9FCD-9520961377F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1365" yWindow="1890" windowWidth="14700" windowHeight="12645" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -837,7 +837,7 @@
         <v>106</v>
       </c>
       <c r="C1" s="6">
-        <v>45484</v>
+        <v>46185</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>32</v>
